--- a/iFST/instructions.xlsx
+++ b/iFST/instructions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github_repos/iFST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="14_{D1FB8DA2-A0B5-464E-9B40-0C34DE3DBC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4E2C856-C289-4475-B363-7525D9CCD11B}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="14_{D1FB8DA2-A0B5-464E-9B40-0C34DE3DBC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{528A1AA9-6BB7-4E8F-928B-A76E280D4C2D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
   <si>
     <t>This is an example sequence. DO NOT practice the sequence at this stage.
 In the image, you can see that each black dot corresponds to a key press. The black line indicates what should be next key press.
@@ -330,6 +330,67 @@
     <t>El objetivo de la tarea es completar la secuencia lo más RÁPIDA y PRECISAMENTE posible, tanto en la ejecución como en la imaginación.
 Sin embargo, te pedimos que PRIORICES LA PRECISIÓN sobre la velocidad. Es decir, intenta completar la tarea lo más rápido posible, asegurándote de completar la secuencia correctamente.
 No es necesario que empieces a escribir o a imaginar inmediatamente después de que comience cada intento, pero cuando empiece el movimiento, intenta completarlo lo más rápido y con la mayor precisión posible.</t>
+  </si>
+  <si>
+    <t>inst_msg_DE</t>
+  </si>
+  <si>
+    <t>In dieser Aufgabe werden Sie zwei 8-stellige Sequenzen mit Ihrer RECHTEN Hand tippen oder sich vorstellen zu tippen. Manchmal werden Sie die Sequenz PHYSISCH tippen. Zu anderen Zeiten werden Sie sich das Tippen der Sequenz nur VORSTELLEN. Während der Vorstellung werden Sie gebeten, sich auf BEIDE der folgenden Aspekte zu konzentrieren:
+VISUELLE Aspekte der Bewegung (d. h. sich vorzustellen, wie Sie Ihre Finger aus einer INTERNEN Perspektive bzw. aus der ICH-PERSPEKTIVE bewegen)
+KINÄSTHETISCHE Aspekte der Bewegung (d. h. sich vorzustellen, wie sich Ihre Muskeln zusammenziehen und sich Ihre Gelenke bewegen)
+Bitte versuchen Sie immer, sich auf BEIDE ASPEKTE GLEICHZEITIG zu konzentrieren, auch wenn sich dies nicht natürlich anfühlt. Falls Ihnen dies schwergefallen ist, haben Sie nach der Aufgabe die Möglichkeit, Ihre Erfahrung zu erläutern.</t>
+  </si>
+  <si>
+    <t>In dieser Aufgabe werden Sie zwei 8-stellige Sequenzen mit Ihrer LINKEN Hand tippen oder sich vorstellen zu tippen. Manchmal werden Sie die Sequenz PHYSISCH tippen. Zu anderen Zeiten werden Sie sich das Tippen der Sequenz nur VORSTELLEN. Während der Vorstellung werden Sie gebeten, sich auf BEIDE der folgenden Aspekte zu konzentrieren:
+VISUELLE Aspekte der Bewegung (d. h. sich vorzustellen, wie Sie Ihre Finger aus einer INTERNEN Perspektive bzw. aus der ICH-PERSPEKTIVE bewegen)
+KINÄSTHETISCHE Aspekte der Bewegung (d. h. sich vorzustellen, wie sich Ihre Muskeln zusammenziehen und sich Ihre Gelenke bewegen)
+Bitte versuchen Sie immer, sich auf BEIDE ASPEKTE GLEICHZEITIG zu konzentrieren, auch wenn sich dies nicht natürlich anfühlt. Falls Ihnen dies schwergefallen ist, haben Sie nach der Aufgabe die Möglichkeit, Ihre Erfahrung zu erläutern.</t>
+  </si>
+  <si>
+    <t>Für die Aufgabe verwenden Sie die vier Finger Ihrer dominanten Hand.
+Bitte legen Sie Ihre RECHTE Hand auf die Tastatur, wobei Ihre Finger auf den angezeigten Tasten liegen:
+F = Zeigefinger
+G = Mittelfinger
+H = Ringfinger
+J = Kleiner Finger
+Bitte halten Sie während der gesamten Aufgabe Ihre Hand in dieser Position.</t>
+  </si>
+  <si>
+    <t>Für die Aufgabe verwenden Sie die vier Finger Ihrer dominanten Hand.
+Bitte legen Sie Ihre Hand auf die Tastatur, wobei Ihre Finger auf den angezeigten Tasten liegen:
+J = Zeigefinger
+H = Mittelfinger
+G = Ringfinger
+F = Kleiner Finger
+Bitte halten Sie während der gesamten Aufgabe Ihre Hand in dieser Position.</t>
+  </si>
+  <si>
+    <t>Dies ist eine Beispielsequenz. ÜBEN Sie die Sequenz zu diesem Zeitpunkt NICHT.
+Im Bild können Sie sehen, dass jeder schwarze Punkt einem Tastendruck entspricht. Die schwarze Linie zeigt an, welcher Tastendruck als Nächstes erfolgen sollte.
+Im Fall dieser Sequenz wäre die korrekte Reihenfolge:
+Zeigefinger-Mittelfinger-Ringfinger-Kleiner Finger-Kleiner Finger-Ringfinger-Mittelfinger-Zeigefinger</t>
+  </si>
+  <si>
+    <t>Dies ist ein weiteres Beispiel für eine Sequenz. ÜBEN Sie die Sequenz zu diesem Zeitpunkt NICHT.
+Hier wäre die korrekte Reihenfolge:
+Zeigefinger-Kleiner Finger-Mittelfinger-Ringfinger-Ringfinger-Mittelfinger-Kleiner Finger-Zeigefinger</t>
+  </si>
+  <si>
+    <t>Wenn Sie die Sequenz PHYSISCH AUSFÜHREN, müssen Sie alle Tasten drücken, um den Durchgang zu beenden.
+Sie sehen in diesem Fall diese Bilder.</t>
+  </si>
+  <si>
+    <t>Wenn Sie sich die Sequenz VORSTELLEN, drücken Sie NUR die ERSTE Taste der Sequenz, STELLEN sich die folgenden Bewegungen vor und drücken anschließend erneut die LETZTE Taste.
+Im gezeigten Beispiel würden Sie:
+Physisch mit dem Zeigefinger drücken.
+Sich das Drücken mit den übrigen Fingern vorstellen.
+Physisch erneut mit dem Zeigefinger drücken.
+Wenn Sie sich die Bewegungen vorstellen, BEWEGEN Sie Ihre Hand NICHT, halten Sie sie ruhig über den angegebenen Tasten.</t>
+  </si>
+  <si>
+    <t>Ziel der Aufgabe ist es, die Sequenz sowohl bei der Ausführung als auch bei der Vorstellung so SCHNELL und GENAU wie möglich zu absolvieren.
+Wir bitten Sie jedoch, die GENAUIGKEIT gegenüber der Geschwindigkeit zu PRIORISIEREN. Das heißt, versuchen Sie, die Aufgabe so schnell wie möglich zu erledigen, während Sie sicherstellen, dass Sie die Sequenz korrekt ausführen.
+Sie müssen nicht sofort nach Beginn des Durchgangs mit dem Tippen oder Vorstellen beginnen, aber sobald Sie die Bewegung starten, versuchen Sie, sie so schnell und genau wie möglich abzuschließen.</t>
   </si>
 </sst>
 </file>
@@ -433,10 +494,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -736,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.7265625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.36328125" style="1" customWidth="1"/>
@@ -747,7 +804,7 @@
     <col min="6" max="6" width="29.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -772,8 +829,11 @@
       <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -798,8 +858,11 @@
       <c r="H2" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="I2" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -824,8 +887,11 @@
       <c r="H3" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="I3" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -850,8 +916,11 @@
       <c r="H4" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="I4" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -876,8 +945,11 @@
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="I5" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -902,8 +974,11 @@
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="I6" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -928,8 +1003,11 @@
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="I7" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -954,8 +1032,11 @@
       <c r="H8" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="I8" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -980,8 +1061,11 @@
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="I9" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="10" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1006,8 +1090,11 @@
       <c r="H10" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="I10" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="11" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1032,8 +1119,11 @@
       <c r="H11" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="I11" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="12" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1058,8 +1148,11 @@
       <c r="H12" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="I12" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="13" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1177,11 @@
       <c r="H13" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="I13" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="14" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1109,6 +1205,9 @@
       </c>
       <c r="H14" s="3" t="s">
         <v>36</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1131,6 +1230,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -1244,15 +1352,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
@@ -1269,6 +1368,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1282,12 +1389,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>